--- a/AAII_Financials/Yearly/NGG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NGG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>NGG</t>
   </si>
@@ -656,126 +656,132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23355200</v>
+      </c>
+      <c r="E8" s="3">
         <v>23744500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25070100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26795100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24251400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18825400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16633300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19446800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21405000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19171100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16393400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16294200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20956400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17684500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18041200</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -803,75 +809,81 @@
       <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="3">
         <v>4845400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4320500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5172400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6414700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4518700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7098100</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>23355200</v>
+      </c>
+      <c r="E10" s="3">
         <v>23744500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25070100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26795100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24251400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18825400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16633300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19446800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21405000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14325700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12073000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11121800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14541700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13165800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10943200</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -890,56 +902,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E12" s="3">
         <v>55600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>40400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>28500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19600</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -985,105 +1001,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-499100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-55600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1271800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-904300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-198500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>51000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>517900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>905100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>71600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>807100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>159800</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-219200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>397800</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2452100</v>
+      </c>
+      <c r="E15" s="3">
         <v>2330800</v>
       </c>
-      <c r="E15" s="3">
-        <v>2133200</v>
-      </c>
       <c r="F15" s="3">
+        <v>2603000</v>
+      </c>
+      <c r="G15" s="3">
         <v>2022700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2405600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1620100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1601100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2018500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2147500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1888400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1626700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1451700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2003800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1676200</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1099,104 +1124,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16529700</v>
+      </c>
+      <c r="E17" s="3">
         <v>17297400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18015100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21592900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18723900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15505300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13340200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14813300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16419400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15080600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12391900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12854100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15670900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13067300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13430500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6825500</v>
+      </c>
+      <c r="E18" s="3">
         <v>6447100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7055000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5202100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5527500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3320100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3293000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4633500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4985600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4090500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4001600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3440100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5285400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4617300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4610700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1215,248 +1247,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>134700</v>
+      </c>
+      <c r="E20" s="3">
         <v>58100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>63100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-204100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-176100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-38600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-13700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>140600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-147400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-177200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-279200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-89100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>49500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-114800</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9142900</v>
+      </c>
+      <c r="E21" s="3">
         <v>8719800</v>
       </c>
-      <c r="E21" s="3">
-        <v>9125000</v>
-      </c>
       <c r="F21" s="3">
+        <v>9594800</v>
+      </c>
+      <c r="G21" s="3">
         <v>7429000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8109200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4978800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4907800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6511300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7280500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5808400</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4823500</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6231500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6186800</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2015000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2170600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2047300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1969500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1424900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1063500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1108100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1263200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1403600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1128500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>832600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>960100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1446200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1225400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1389100</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5522200</v>
+      </c>
+      <c r="E23" s="3">
         <v>4715800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3849600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4441300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4523200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2292400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1743000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2397500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3733600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2784800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2889800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2391000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3888700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3338900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3106900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1239900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1060700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1049500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1083700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1653700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>495900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>460700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>441500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1247800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>476900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>529800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>569700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>401900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>686000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>603900</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1502,105 +1550,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4282300</v>
+      </c>
+      <c r="E26" s="3">
         <v>3655100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2800000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3357600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2869600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1796400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1282400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1956000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4981400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2307900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2360000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1821300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3486800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2652900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2503000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4279600</v>
+      </c>
+      <c r="E27" s="3">
         <v>3749400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2892200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9645900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3093000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2259300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1573700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1967700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4982800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2307900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2358800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1833500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3503800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2651600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2500400</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1646,47 +1703,50 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>98200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>93500</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>6288400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>224800</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>464300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>292600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>15600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>2800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>7631500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>856200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>629500</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>10</v>
@@ -1694,9 +1754,12 @@
       <c r="Q29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1742,9 +1805,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1790,105 +1856,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-134700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-58100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-63100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>204100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>176100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>38600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>13700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-140600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>147400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>177200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>279200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>89100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-49500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>53000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>114800</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4279600</v>
+      </c>
+      <c r="E33" s="3">
         <v>3749400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2892200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9645900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3093000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2259300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1573700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1967700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4982800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9939400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3214900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2463000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3503800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2651600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2500400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1934,110 +2009,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4279600</v>
+      </c>
+      <c r="E35" s="3">
         <v>3749400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2892200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9645900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3093000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2259300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1573700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1967700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4982800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9939400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3214900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2463000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3503800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2651600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2500400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2056,8 +2140,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2076,440 +2161,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>495200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1522000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>706000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>201700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>268200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>216300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>90900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>328200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>461800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1452300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>157600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>145200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>500900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>828300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>433000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3239100</v>
+      </c>
+      <c r="E42" s="3">
         <v>7432900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4671800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3222700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4134100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3226400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2487500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2579800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3781300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11145600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3719900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3121700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5093000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12186000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3118600</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4683700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4861800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3840700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4310200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4458800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3580500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3336600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4270100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3765900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6161300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2776900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2098200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2438200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4643800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1269100</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>738100</v>
+      </c>
+      <c r="E44" s="3">
         <v>719600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1045700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>915500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>516600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>478000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>517900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>481800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>376200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>513900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>542200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>414800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>379200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>369100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>490400</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>283900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3541400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2358000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2142700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13670900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5656600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>281400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2687900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>670900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>673300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>635300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1577300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2186300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2142900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1715200</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9883700</v>
+      </c>
+      <c r="E46" s="3">
         <v>18517000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13108400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11274000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23612500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13691000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7222300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10347800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9377500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17308200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7831900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7357200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10597800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11820600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7026300</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1935800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1816600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2904800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2671000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2718400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2234500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1914800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1660400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4304900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4116000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1136600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>838100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>945300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>927000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>842600</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>107644900</v>
+      </c>
+      <c r="E48" s="3">
         <v>95726000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>87028000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>79712200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>75626400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>64808200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>61953900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>58418500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>55938000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50780900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>53806100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>49678000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>52612400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25589100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43956600</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17557000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16920100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16620800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16640700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16831000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8308500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8723700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8407500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8903100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8949900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7695400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7254700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7447700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7660700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6941500</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2555,9 +2668,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2603,57 +2719,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5960600</v>
+      </c>
+      <c r="E52" s="3">
         <v>4931600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4520200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4380700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5906100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3557100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4297800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3745300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3990500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2863900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2655300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2075000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2526000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2805800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2972500</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2699,57 +2821,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>142982000</v>
+      </c>
+      <c r="E54" s="3">
         <v>137911300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>124182200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>114678600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>124694400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>92599300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>84112500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>82579500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>82513900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>83952600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>73125300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>67203100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>74129100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>67527900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>61739500</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2768,8 +2896,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2788,296 +2917,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4455300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3830800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3518700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4019400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4092100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2982600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2745200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4908300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2774900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2722300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2528800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2500800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2748100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5019100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1995600</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5462800</v>
+      </c>
+      <c r="E58" s="3">
         <v>6482000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6451300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3770800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16111900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5244700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5385900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5823800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6698000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7007900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4480500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3693900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4968500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4811700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3250300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2893200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3240400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4414100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3207900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11991000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4485600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2279600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1156400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2491400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3790900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2570900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2800900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2657600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2424400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2585100</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12936700</v>
+      </c>
+      <c r="E60" s="3">
         <v>13722400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14384000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11295000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32560400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12905700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10662200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11888400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12207200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13402600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9580200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8995500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10374200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9190100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7831100</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>57530300</v>
+      </c>
+      <c r="E61" s="3">
         <v>56409000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>54421700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>50791800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>44954900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>38821800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>34364600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31590500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31999400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>29508400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>30688700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27913800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31753700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>30424300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>26781400</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4596600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4651200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4688200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4003400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4044700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3842200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3946700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4589200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4241700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15050000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16024900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15686700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15134600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15280600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15067400</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3123,9 +3271,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3171,9 +3322,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3219,57 +3373,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91047900</v>
+      </c>
+      <c r="E66" s="3">
         <v>89039900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86429300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78106400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>93335400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>65239400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>59470100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57096700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>56058700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57981300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>56306300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>52610600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>57273700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>54901200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>49689000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3288,8 +3448,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3335,9 +3496,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3383,9 +3547,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3431,9 +3598,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3479,57 +3649,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>55339700</v>
+      </c>
+      <c r="E72" s="3">
         <v>51817200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>40498600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>39103300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>34980400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>31910200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27259400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28648600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30316500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22232600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13846100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11862300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13795900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9771500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9196700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3575,9 +3751,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3623,9 +3802,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3671,57 +3853,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51893200</v>
+      </c>
+      <c r="E76" s="3">
         <v>48841700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>37721300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>36542500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>31328700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>27331000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24615000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25456800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26432700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25971200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16819000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14592400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16855400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12626700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12050500</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3767,110 +3955,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4279600</v>
+      </c>
+      <c r="E81" s="3">
         <v>3749400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2892200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9645900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3093000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2259300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1573700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1967700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4982800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9939400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3214900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2463000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3503800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2651600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2500400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3889,56 +4086,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2626400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2485800</v>
       </c>
-      <c r="E83" s="3">
-        <v>2278400</v>
-      </c>
       <c r="F83" s="3">
+        <v>2603000</v>
+      </c>
+      <c r="G83" s="3">
         <v>2183500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2405600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1775800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1601100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2018500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2147500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1888400</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1466300</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1676200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1672100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3984,9 +4185,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4032,9 +4236,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4080,9 +4287,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4128,9 +4338,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4176,57 +4389,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10338000</v>
+      </c>
+      <c r="E89" s="3">
         <v>8796000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8763800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8533700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8244600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6145600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5749400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5623200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6320400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6686600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6212700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6108000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5687300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4618500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5514600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4245,56 +4464,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13190200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11343800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8719600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7824900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6701400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5798500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5342300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4733800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5246700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4202700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3198800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3144900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4166100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3958400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4104700</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4340,9 +4563,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4388,57 +4614,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5489200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13657800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9471100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>296900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18416300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7048000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3977800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4487600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3603100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5500800</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2441000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7549700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3092500</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4457,56 +4689,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2143100</v>
+      </c>
+      <c r="E96" s="3">
         <v>1975500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2169800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1988100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1212000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1946600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1110500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1510600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1847100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1865500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1577100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1550500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1498600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-997600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1312100</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4552,9 +4788,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4600,9 +4839,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4648,151 +4890,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6100600</v>
+      </c>
+      <c r="E100" s="3">
         <v>5850200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1246600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8874000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10212400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1033200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1999500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1239800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11056200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>88000</v>
       </c>
-      <c r="M100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3968300</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3343800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2478200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-29700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>8700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>20400</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>29300</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>17200</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1262400</v>
+      </c>
+      <c r="E102" s="3">
         <v>958700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>538000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-34600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>47300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>121200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-222900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1136900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1294200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-276700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-272000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-437300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>429800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-56100</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
